--- a/report_9.xlsx
+++ b/report_9.xlsx
@@ -7442,7 +7442,7 @@
         <v>41890</v>
       </c>
       <c r="E2" t="n">
-        <v>4240</v>
+        <v>4245</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -7468,7 +7468,7 @@
         <v>42015</v>
       </c>
       <c r="E3" t="n">
-        <v>4115</v>
+        <v>4120</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -7494,7 +7494,7 @@
         <v>42071</v>
       </c>
       <c r="E4" t="n">
-        <v>4059</v>
+        <v>4064</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -7520,7 +7520,7 @@
         <v>42287</v>
       </c>
       <c r="E5" t="n">
-        <v>3843</v>
+        <v>3848</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -7546,7 +7546,7 @@
         <v>42529</v>
       </c>
       <c r="E6" t="n">
-        <v>3601</v>
+        <v>3606</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         <v>42530</v>
       </c>
       <c r="E7" t="n">
-        <v>3600</v>
+        <v>3605</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -7598,7 +7598,7 @@
         <v>42740</v>
       </c>
       <c r="E8" t="n">
-        <v>3390</v>
+        <v>3395</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -7624,7 +7624,7 @@
         <v>42948</v>
       </c>
       <c r="E9" t="n">
-        <v>3182</v>
+        <v>3187</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -7650,7 +7650,7 @@
         <v>43354</v>
       </c>
       <c r="E10" t="n">
-        <v>2776</v>
+        <v>2781</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -7676,7 +7676,7 @@
         <v>43380</v>
       </c>
       <c r="E11" t="n">
-        <v>2750</v>
+        <v>2755</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -7702,7 +7702,7 @@
         <v>43531</v>
       </c>
       <c r="E12" t="n">
-        <v>2599</v>
+        <v>2604</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -7728,7 +7728,7 @@
         <v>43656</v>
       </c>
       <c r="E13" t="n">
-        <v>2474</v>
+        <v>2479</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -7754,7 +7754,7 @@
         <v>43746</v>
       </c>
       <c r="E14" t="n">
-        <v>2384</v>
+        <v>2389</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -7780,7 +7780,7 @@
         <v>43811</v>
       </c>
       <c r="E15" t="n">
-        <v>2319</v>
+        <v>2324</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -7806,7 +7806,7 @@
         <v>43893</v>
       </c>
       <c r="E16" t="n">
-        <v>2237</v>
+        <v>2242</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -7832,7 +7832,7 @@
         <v>44076</v>
       </c>
       <c r="E17" t="n">
-        <v>2054</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -7858,7 +7858,7 @@
         <v>44139</v>
       </c>
       <c r="E18" t="n">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -7884,7 +7884,7 @@
         <v>44199</v>
       </c>
       <c r="E19" t="n">
-        <v>1931</v>
+        <v>1936</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -7910,7 +7910,7 @@
         <v>44200</v>
       </c>
       <c r="E20" t="n">
-        <v>1930</v>
+        <v>1935</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -7936,7 +7936,7 @@
         <v>44202</v>
       </c>
       <c r="E21" t="n">
-        <v>1928</v>
+        <v>1933</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -7962,7 +7962,7 @@
         <v>44258</v>
       </c>
       <c r="E22" t="n">
-        <v>1872</v>
+        <v>1877</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -7988,7 +7988,7 @@
         <v>44359</v>
       </c>
       <c r="E23" t="n">
-        <v>1771</v>
+        <v>1776</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -8014,7 +8014,7 @@
         <v>44379</v>
       </c>
       <c r="E24" t="n">
-        <v>1751</v>
+        <v>1756</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -8040,7 +8040,7 @@
         <v>44389</v>
       </c>
       <c r="E25" t="n">
-        <v>1741</v>
+        <v>1746</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -8066,7 +8066,7 @@
         <v>44412</v>
       </c>
       <c r="E26" t="n">
-        <v>1718</v>
+        <v>1723</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -8092,7 +8092,7 @@
         <v>44474</v>
       </c>
       <c r="E27" t="n">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -8118,7 +8118,7 @@
         <v>44567</v>
       </c>
       <c r="E28" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -8144,7 +8144,7 @@
         <v>44630</v>
       </c>
       <c r="E29" t="n">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -8170,7 +8170,7 @@
         <v>44655</v>
       </c>
       <c r="E30" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -8196,7 +8196,7 @@
         <v>44685</v>
       </c>
       <c r="E31" t="n">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -8222,7 +8222,7 @@
         <v>44719</v>
       </c>
       <c r="E32" t="n">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -8248,7 +8248,7 @@
         <v>44720</v>
       </c>
       <c r="E33" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -8274,7 +8274,7 @@
         <v>44720</v>
       </c>
       <c r="E34" t="n">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -8300,7 +8300,7 @@
         <v>44777</v>
       </c>
       <c r="E35" t="n">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -8326,7 +8326,7 @@
         <v>44777</v>
       </c>
       <c r="E36" t="n">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -8352,7 +8352,7 @@
         <v>44782</v>
       </c>
       <c r="E37" t="n">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>44846</v>
       </c>
       <c r="E38" t="n">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -8404,7 +8404,7 @@
         <v>44902</v>
       </c>
       <c r="E39" t="n">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -8430,7 +8430,7 @@
         <v>44987</v>
       </c>
       <c r="E40" t="n">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -8456,7 +8456,7 @@
         <v>45019</v>
       </c>
       <c r="E41" t="n">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -8482,7 +8482,7 @@
         <v>45025</v>
       </c>
       <c r="E42" t="n">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -8508,7 +8508,7 @@
         <v>45082</v>
       </c>
       <c r="E43" t="n">
-        <v>1048</v>
+        <v>1053</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -8534,7 +8534,7 @@
         <v>45233</v>
       </c>
       <c r="E44" t="n">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -8560,7 +8560,7 @@
         <v>45262</v>
       </c>
       <c r="E45" t="n">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -8586,7 +8586,7 @@
         <v>45267</v>
       </c>
       <c r="E46" t="n">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -8612,7 +8612,7 @@
         <v>45268</v>
       </c>
       <c r="E47" t="n">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -8638,7 +8638,7 @@
         <v>45295</v>
       </c>
       <c r="E48" t="n">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -8664,7 +8664,7 @@
         <v>45323</v>
       </c>
       <c r="E49" t="n">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -8690,7 +8690,7 @@
         <v>45334</v>
       </c>
       <c r="E50" t="n">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -8716,7 +8716,7 @@
         <v>45354</v>
       </c>
       <c r="E51" t="n">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -8742,7 +8742,7 @@
         <v>45356</v>
       </c>
       <c r="E52" t="n">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -8768,7 +8768,7 @@
         <v>45357</v>
       </c>
       <c r="E53" t="n">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -8794,7 +8794,7 @@
         <v>45359</v>
       </c>
       <c r="E54" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -8820,7 +8820,7 @@
         <v>45360</v>
       </c>
       <c r="E55" t="n">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -8846,7 +8846,7 @@
         <v>45361</v>
       </c>
       <c r="E56" t="n">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -8872,7 +8872,7 @@
         <v>45384</v>
       </c>
       <c r="E57" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -8898,7 +8898,7 @@
         <v>45385</v>
       </c>
       <c r="E58" t="n">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -8924,7 +8924,7 @@
         <v>45388</v>
       </c>
       <c r="E59" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -8950,7 +8950,7 @@
         <v>45448</v>
       </c>
       <c r="E60" t="n">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -8976,7 +8976,7 @@
         <v>45452</v>
       </c>
       <c r="E61" t="n">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -9002,7 +9002,7 @@
         <v>45483</v>
       </c>
       <c r="E62" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -9028,7 +9028,7 @@
         <v>45483</v>
       </c>
       <c r="E63" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -9054,7 +9054,7 @@
         <v>45509</v>
       </c>
       <c r="E64" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>45575</v>
       </c>
       <c r="E65" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -9106,7 +9106,7 @@
         <v>45600</v>
       </c>
       <c r="E66" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -9132,7 +9132,7 @@
         <v>45602</v>
       </c>
       <c r="E67" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -9158,7 +9158,7 @@
         <v>45605</v>
       </c>
       <c r="E68" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -9184,7 +9184,7 @@
         <v>45627</v>
       </c>
       <c r="E69" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         <v>45637</v>
       </c>
       <c r="E70" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -9236,7 +9236,7 @@
         <v>45638</v>
       </c>
       <c r="E71" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -9262,7 +9262,7 @@
         <v>45660</v>
       </c>
       <c r="E72" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -9288,7 +9288,7 @@
         <v>45662</v>
       </c>
       <c r="E73" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -9314,7 +9314,7 @@
         <v>45669</v>
       </c>
       <c r="E74" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -9340,7 +9340,7 @@
         <v>45669</v>
       </c>
       <c r="E75" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -9366,7 +9366,7 @@
         <v>45700</v>
       </c>
       <c r="E76" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -9392,7 +9392,7 @@
         <v>45754</v>
       </c>
       <c r="E77" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -9418,7 +9418,7 @@
         <v>45815</v>
       </c>
       <c r="E78" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -9444,7 +9444,7 @@
         <v>45815</v>
       </c>
       <c r="E79" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -9470,7 +9470,7 @@
         <v>45845</v>
       </c>
       <c r="E80" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -9496,7 +9496,7 @@
         <v>45876</v>
       </c>
       <c r="E81" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -9522,7 +9522,7 @@
         <v>45877</v>
       </c>
       <c r="E82" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -9548,7 +9548,7 @@
         <v>45939</v>
       </c>
       <c r="E83" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -9574,7 +9574,7 @@
         <v>45941</v>
       </c>
       <c r="E84" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         <v>45941</v>
       </c>
       <c r="E85" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -9626,7 +9626,7 @@
         <v>45969</v>
       </c>
       <c r="E86" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -9652,7 +9652,7 @@
         <v>45970</v>
       </c>
       <c r="E87" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>46002</v>
       </c>
       <c r="E88" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -9704,7 +9704,7 @@
         <v>46023</v>
       </c>
       <c r="E89" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -9730,7 +9730,7 @@
         <v>46062</v>
       </c>
       <c r="E90" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -9756,7 +9756,7 @@
         <v>46083</v>
       </c>
       <c r="E91" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -9782,7 +9782,7 @@
         <v>46087</v>
       </c>
       <c r="E92" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -9808,7 +9808,7 @@
         <v>46113</v>
       </c>
       <c r="E93" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -9834,7 +9834,7 @@
         <v>46114</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -9860,7 +9860,7 @@
         <v>46114</v>
       </c>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -9886,7 +9886,7 @@
         <v>46120</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -31392,7 +31392,7 @@
         <v>46144</v>
       </c>
       <c r="E992" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="F992" t="b">
         <v>0</v>
@@ -31418,7 +31418,7 @@
         <v>46149</v>
       </c>
       <c r="E993" t="n">
-        <v>-19</v>
+        <v>-14</v>
       </c>
       <c r="F993" t="b">
         <v>0</v>
@@ -31444,7 +31444,7 @@
         <v>46149</v>
       </c>
       <c r="E994" t="n">
-        <v>-19</v>
+        <v>-14</v>
       </c>
       <c r="F994" t="b">
         <v>0</v>
@@ -31470,7 +31470,7 @@
         <v>46152</v>
       </c>
       <c r="E995" t="n">
-        <v>-22</v>
+        <v>-17</v>
       </c>
       <c r="F995" t="b">
         <v>1</v>
@@ -31496,7 +31496,7 @@
         <v>46176</v>
       </c>
       <c r="E996" t="n">
-        <v>-46</v>
+        <v>-41</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -31522,7 +31522,7 @@
         <v>46177</v>
       </c>
       <c r="E997" t="n">
-        <v>-47</v>
+        <v>-42</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -31548,7 +31548,7 @@
         <v>46205</v>
       </c>
       <c r="E998" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -31574,7 +31574,7 @@
         <v>46210</v>
       </c>
       <c r="E999" t="n">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -31600,7 +31600,7 @@
         <v>46235</v>
       </c>
       <c r="E1000" t="n">
-        <v>-105</v>
+        <v>-100</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -31626,7 +31626,7 @@
         <v>46244</v>
       </c>
       <c r="E1001" t="n">
-        <v>-114</v>
+        <v>-109</v>
       </c>
       <c r="F1001" t="b">
         <v>1</v>
@@ -31652,7 +31652,7 @@
         <v>46358</v>
       </c>
       <c r="E1002" t="n">
-        <v>-228</v>
+        <v>-223</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
